--- a/uploads/processed_64192_FCL_Express_S.r.l_contract.xlsx
+++ b/uploads/processed_64192_FCL_Express_S.r.l_contract.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG76"/>
+  <dimension ref="A1:AG53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.3984375" defaultRowHeight="15.6"/>
   <cols>
     <col width="9.3984375" customWidth="1" style="1" min="1" max="5"/>
@@ -672,12 +672,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>USCHS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>USATL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -715,16 +715,11 @@
         <v>46023</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -736,12 +731,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAVANNAH</t>
+          <t>USCHS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>USBHM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -751,7 +746,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -765,10 +760,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J4" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -779,16 +774,11 @@
         <v>46023</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -800,12 +790,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>USSAV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>USCLT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -815,7 +805,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="J5" t="n">
-        <v>1200</v>
+        <v>940</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -843,16 +833,11 @@
         <v>46023</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -864,12 +849,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SAVANNAH</t>
+          <t>USCHS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>USCLT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -879,7 +864,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -893,10 +878,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="J6" t="n">
-        <v>1200</v>
+        <v>940</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -907,16 +892,11 @@
         <v>46023</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -928,12 +908,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAVANNAH</t>
+          <t>USNYC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>USCHI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -943,7 +923,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -957,10 +937,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>800</v>
+        <v>1180</v>
       </c>
       <c r="J7" t="n">
-        <v>940</v>
+        <v>1150</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -971,16 +951,11 @@
         <v>46023</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -992,12 +967,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>CAMTR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>USCHI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1007,7 +982,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1021,10 +996,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>900</v>
+        <v>1190</v>
       </c>
       <c r="J8" t="n">
-        <v>940</v>
+        <v>1350</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1035,16 +1010,11 @@
         <v>46023</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1056,12 +1026,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>USCLE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1071,7 +1041,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1085,10 +1055,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1180</v>
+        <v>1190</v>
       </c>
       <c r="J9" t="n">
-        <v>1150</v>
+        <v>1190</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1099,16 +1069,11 @@
         <v>46023</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1120,12 +1085,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>USCMH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1135,7 +1100,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1149,10 +1114,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1180</v>
+        <v>2200</v>
       </c>
       <c r="J10" t="n">
-        <v>1150</v>
+        <v>2450</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1163,16 +1128,11 @@
         <v>46023</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1184,12 +1144,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MONTREAL</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>USCBF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1199,7 +1159,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1213,10 +1173,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1190</v>
+        <v>2650</v>
       </c>
       <c r="J11" t="n">
-        <v>1350</v>
+        <v>2900</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1227,16 +1187,11 @@
         <v>46023</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1248,12 +1203,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USHOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>USDEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1263,7 +1218,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1280,7 +1235,7 @@
         <v>1190</v>
       </c>
       <c r="J12" t="n">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1291,16 +1246,11 @@
         <v>46023</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1312,12 +1262,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>USDET</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1327,7 +1277,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1341,10 +1291,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1190</v>
+        <v>1500</v>
       </c>
       <c r="J13" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1355,16 +1305,11 @@
         <v>46023</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -1376,12 +1321,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USNYC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>USESL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1391,7 +1336,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1405,10 +1350,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1190</v>
+        <v>1100</v>
       </c>
       <c r="J14" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1419,21 +1364,11 @@
         <v>46023</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>AMN 22</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -1445,12 +1380,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>USESL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1460,7 +1395,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1474,10 +1409,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1190</v>
+        <v>1690</v>
       </c>
       <c r="J15" t="n">
-        <v>1190</v>
+        <v>1590</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1488,21 +1423,11 @@
         <v>46023</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>AMN 22</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -1514,12 +1439,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USCHS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>USGXX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1529,7 +1454,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1543,10 +1468,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1190</v>
+        <v>1590</v>
       </c>
       <c r="J16" t="n">
-        <v>1190</v>
+        <v>1700</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1557,16 +1482,11 @@
         <v>46023</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -1578,12 +1498,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USNYC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Columbus</t>
+          <t>USMKC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1593,7 +1513,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1607,10 +1527,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2200</v>
+        <v>1300</v>
       </c>
       <c r="J17" t="n">
-        <v>2450</v>
+        <v>1550</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1621,16 +1541,11 @@
         <v>46023</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -1642,12 +1557,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Council Bluffs</t>
+          <t>USLUI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1657,7 +1572,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1671,10 +1586,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="J18" t="n">
-        <v>2450</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1685,16 +1600,11 @@
         <v>46023</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -1706,12 +1616,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USNYC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Council Bluffs</t>
+          <t>USLUI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1721,7 +1631,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1735,10 +1645,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2650</v>
+        <v>1190</v>
       </c>
       <c r="J19" t="n">
-        <v>2900</v>
+        <v>1260</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -1749,16 +1659,11 @@
         <v>46023</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -1770,12 +1675,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HOUSTON</t>
+          <t>USMSY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Denver</t>
+          <t>USMEM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1785,7 +1690,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1799,10 +1704,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1190</v>
+        <v>1350</v>
       </c>
       <c r="J20" t="n">
-        <v>1250</v>
+        <v>1380</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -1813,16 +1718,11 @@
         <v>46023</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -1834,12 +1734,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>USCHS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>USBNA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1849,7 +1749,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1863,10 +1763,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1190</v>
+        <v>2280</v>
       </c>
       <c r="J21" t="n">
-        <v>1250</v>
+        <v>2480</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -1877,16 +1777,11 @@
         <v>46023</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -1898,12 +1793,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NORFOLK</t>
+          <t>USNYC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>USSTP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1913,7 +1808,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1927,10 +1822,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1500</v>
+        <v>1970</v>
       </c>
       <c r="J22" t="n">
-        <v>1550</v>
+        <v>2710</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -1941,16 +1836,11 @@
         <v>46023</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -1962,12 +1852,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MONTREAL</t>
+          <t>USORF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Detroit</t>
+          <t>USSTP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1977,7 +1867,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1991,10 +1881,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1500</v>
+        <v>1795</v>
       </c>
       <c r="J23" t="n">
-        <v>1550</v>
+        <v>2560</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2005,16 +1895,11 @@
         <v>46023</v>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>AMN</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -2026,12 +1911,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>CAMTR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>East Saint Louis</t>
+          <t>USSTP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2041,7 +1926,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>Inland Haulage</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2055,10 +1940,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1100</v>
+        <v>2155</v>
       </c>
       <c r="J24" t="n">
-        <v>1200</v>
+        <v>2155</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2069,18 +1954,13 @@
         <v>46023</v>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG24" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2088,41 +1968,26 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>East Saint Louis</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1690</v>
+        <v>900</v>
       </c>
       <c r="J25" t="n">
-        <v>1590</v>
+        <v>900</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2133,18 +1998,13 @@
         <v>46023</v>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG25" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2152,41 +2012,26 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Greer</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1590</v>
+        <v>900</v>
       </c>
       <c r="J26" t="n">
-        <v>1700</v>
+        <v>900</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2197,18 +2042,13 @@
         <v>46023</v>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2216,41 +2056,26 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1590</v>
+        <v>1200</v>
       </c>
       <c r="J27" t="n">
-        <v>1700</v>
+        <v>1200</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2261,18 +2086,13 @@
         <v>46023</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2280,41 +2100,26 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="J28" t="n">
-        <v>1550</v>
+        <v>1200</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -2325,23 +2130,13 @@
         <v>46023</v>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>AMN 17</t>
-        </is>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2349,41 +2144,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="J29" t="n">
-        <v>1550</v>
+        <v>940</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -2394,18 +2174,13 @@
         <v>46023</v>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG29" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2413,41 +2188,26 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I30" t="n">
         <v>900</v>
       </c>
       <c r="J30" t="n">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -2458,18 +2218,13 @@
         <v>46023</v>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG30" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2477,41 +2232,26 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="J31" t="n">
-        <v>1260</v>
+        <v>1150</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -2522,18 +2262,13 @@
         <v>46023</v>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG31" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2541,41 +2276,26 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MOBILE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>900</v>
+        <v>1180</v>
       </c>
       <c r="J32" t="n">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -2586,18 +2306,13 @@
         <v>46023</v>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG32" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2605,41 +2320,26 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I33" t="n">
         <v>1190</v>
       </c>
       <c r="J33" t="n">
-        <v>1260</v>
+        <v>1350</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -2650,18 +2350,13 @@
         <v>46023</v>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG33" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2669,41 +2364,26 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEW ORLEANS</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I34" t="n">
+        <v>1190</v>
+      </c>
+      <c r="J34" t="n">
         <v>1350</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1380</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -2714,18 +2394,13 @@
         <v>46023</v>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG34" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2733,41 +2408,26 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I35" t="n">
+        <v>1190</v>
+      </c>
+      <c r="J35" t="n">
         <v>1350</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1380</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -2778,18 +2438,13 @@
         <v>46023</v>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG35" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2797,41 +2452,26 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2280</v>
+        <v>1190</v>
       </c>
       <c r="J36" t="n">
-        <v>2480</v>
+        <v>1350</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -2842,16 +2482,16 @@
         <v>46023</v>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>AMN</t>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>AMN 22</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -2861,41 +2501,26 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2280</v>
+        <v>1190</v>
       </c>
       <c r="J37" t="n">
-        <v>2480</v>
+        <v>1190</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -2906,16 +2531,16 @@
         <v>46023</v>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>AMN</t>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>AMN 22</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -2925,41 +2550,26 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1970</v>
+        <v>1190</v>
       </c>
       <c r="J38" t="n">
-        <v>2710</v>
+        <v>1190</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -2970,18 +2580,13 @@
         <v>46023</v>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG38" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -2989,41 +2594,26 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1795</v>
+        <v>2200</v>
       </c>
       <c r="J39" t="n">
-        <v>2560</v>
+        <v>2450</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -3034,18 +2624,13 @@
         <v>46023</v>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG39" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3053,41 +2638,26 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>900</v>
+        <v>2200</v>
       </c>
       <c r="J40" t="n">
-        <v>900</v>
+        <v>2450</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -3095,7 +2665,7 @@
         </is>
       </c>
       <c r="Z40" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA40" s="4" t="n">
         <v>46203</v>
@@ -3105,11 +2675,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG40" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3117,41 +2682,26 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>900</v>
+        <v>2650</v>
       </c>
       <c r="J41" t="n">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -3159,7 +2709,7 @@
         </is>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA41" s="4" t="n">
         <v>46203</v>
@@ -3169,11 +2719,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG41" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3181,41 +2726,26 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="J42" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -3223,7 +2753,7 @@
         </is>
       </c>
       <c r="Z42" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA42" s="4" t="n">
         <v>46203</v>
@@ -3233,11 +2763,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG42" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3245,41 +2770,26 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="J43" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -3287,7 +2797,7 @@
         </is>
       </c>
       <c r="Z43" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA43" s="4" t="n">
         <v>46203</v>
@@ -3297,11 +2807,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG43" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3309,41 +2814,26 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="J44" t="n">
-        <v>940</v>
+        <v>1550</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -3351,7 +2841,7 @@
         </is>
       </c>
       <c r="Z44" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA44" s="4" t="n">
         <v>46203</v>
@@ -3361,11 +2851,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG44" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3373,41 +2858,26 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="J45" t="n">
-        <v>940</v>
+        <v>1550</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -3415,7 +2885,7 @@
         </is>
       </c>
       <c r="Z45" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA45" s="4" t="n">
         <v>46203</v>
@@ -3425,11 +2895,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG45" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3437,41 +2902,26 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1180</v>
+        <v>1100</v>
       </c>
       <c r="J46" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -3479,7 +2929,7 @@
         </is>
       </c>
       <c r="Z46" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA46" s="4" t="n">
         <v>46203</v>
@@ -3489,11 +2939,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG46" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3501,41 +2946,26 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1180</v>
+        <v>1690</v>
       </c>
       <c r="J47" t="n">
-        <v>1150</v>
+        <v>1590</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -3543,7 +2973,7 @@
         </is>
       </c>
       <c r="Z47" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA47" s="4" t="n">
         <v>46203</v>
@@ -3553,11 +2983,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG47" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3565,41 +2990,26 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MONTREAL</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1190</v>
+        <v>1590</v>
       </c>
       <c r="J48" t="n">
-        <v>1350</v>
+        <v>1700</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -3607,7 +3017,7 @@
         </is>
       </c>
       <c r="Z48" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA48" s="4" t="n">
         <v>46203</v>
@@ -3617,11 +3027,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG48" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3629,41 +3034,26 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1190</v>
+        <v>1590</v>
       </c>
       <c r="J49" t="n">
-        <v>1350</v>
+        <v>1700</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -3671,7 +3061,7 @@
         </is>
       </c>
       <c r="Z49" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA49" s="4" t="n">
         <v>46203</v>
@@ -3681,11 +3071,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG49" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3693,41 +3078,26 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1190</v>
+        <v>1300</v>
       </c>
       <c r="J50" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -3735,7 +3105,7 @@
         </is>
       </c>
       <c r="Z50" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA50" s="4" t="n">
         <v>46203</v>
@@ -3745,9 +3115,9 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>AMN</t>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>AMN 17</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -3757,41 +3127,26 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1190</v>
+        <v>1300</v>
       </c>
       <c r="J51" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -3799,7 +3154,7 @@
         </is>
       </c>
       <c r="Z51" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA51" s="4" t="n">
         <v>46203</v>
@@ -3809,16 +3164,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>AMN 22</t>
-        </is>
-      </c>
       <c r="AG51" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3826,41 +3171,26 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1190</v>
+        <v>900</v>
       </c>
       <c r="J52" t="n">
-        <v>1190</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -3868,7 +3198,7 @@
         </is>
       </c>
       <c r="Z52" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA52" s="4" t="n">
         <v>46203</v>
@@ -3878,16 +3208,6 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>AMN 22</t>
-        </is>
-      </c>
       <c r="AG52" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
@@ -3895,41 +3215,26 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAIL</t>
+          <t>TRUCK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RAMP</t>
+          <t>ON CARRIAGE RAMP</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>USD</t>
+          <t>PER CONTAINER</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>1190</v>
       </c>
       <c r="J53" t="n">
-        <v>1190</v>
+        <v>1260</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -3937,7 +3242,7 @@
         </is>
       </c>
       <c r="Z53" s="4" t="n">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="AA53" s="4" t="n">
         <v>46203</v>
@@ -3947,1489 +3252,7 @@
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
       <c r="AG53" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2450</v>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z54" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA54" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Council Bluffs</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2450</v>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z55" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA55" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Council Bluffs</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>2650</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2900</v>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z56" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA56" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>HOUSTON</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z57" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA57" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z58" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA58" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z59" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA59" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MONTREAL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z60" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA60" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>East Saint Louis</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z61" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA61" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>East Saint Louis</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>1690</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1590</v>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z62" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA62" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Greer</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1700</v>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z63" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA63" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1700</v>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z64" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA64" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z65" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA65" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>AMN 17</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z66" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA66" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>900</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z67" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA67" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1260</v>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z68" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA68" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MOBILE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>900</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z69" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA69" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J70" t="n">
-        <v>1260</v>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z70" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA70" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>NEW ORLEANS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1380</v>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z71" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA71" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Memphis</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1380</v>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z72" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA72" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>2280</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2480</v>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z73" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA73" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Nashville</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>2280</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2480</v>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z74" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA74" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>1970</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2710</v>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z75" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA75" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>NEW ONCARRIAGE RAMP 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Saint Paul</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RAIL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>RAMP</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>PER_CONTAINER</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>1795</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2560</v>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="Z76" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="AA76" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
         <is>
           <t>NEW ONCARRIAGE RAMP 2026</t>
         </is>
@@ -5447,7 +3270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM75"/>
+  <dimension ref="A1:AM48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="19.5" defaultRowHeight="15.6"/>
   <cols>
     <col outlineLevel="1" width="19.5" customWidth="1" min="1" max="11"/>
@@ -5683,7 +3506,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5713,14 +3536,9 @@
       <c r="AC2" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -5767,7 +3585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5797,14 +3615,9 @@
       <c r="AC3" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -5851,7 +3664,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5881,14 +3694,9 @@
       <c r="AC4" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -5925,7 +3733,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5935,7 +3743,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5965,19 +3773,14 @@
       <c r="AC5" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6019,7 +3822,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6049,19 +3852,14 @@
       <c r="AC6" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -6103,7 +3901,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FREIGHT</t>
+          <t>Ocean Freight</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6133,19 +3931,14 @@
       <c r="AC7" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -6217,14 +4010,9 @@
       <c r="AC8" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -6301,14 +4089,9 @@
       <c r="AC9" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -6385,14 +4168,9 @@
       <c r="AC10" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -6429,7 +4207,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6469,19 +4247,14 @@
       <c r="AC11" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -6553,19 +4326,14 @@
       <c r="AC12" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -6637,19 +4405,14 @@
       <c r="AC13" s="4" t="n">
         <v>46173</v>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -6721,14 +4484,9 @@
       <c r="AC14" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -6805,14 +4563,9 @@
       <c r="AC15" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -6889,14 +4642,9 @@
       <c r="AC16" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -6933,7 +4681,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6973,19 +4721,14 @@
       <c r="AC17" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7057,19 +4800,14 @@
       <c r="AC18" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7141,19 +4879,14 @@
       <c r="AC19" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -7225,14 +4958,9 @@
       <c r="AC20" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -7309,14 +5037,9 @@
       <c r="AC21" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -7393,14 +5116,9 @@
       <c r="AC22" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -7437,7 +5155,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7477,19 +5195,14 @@
       <c r="AC23" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -7561,19 +5274,14 @@
       <c r="AC24" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -7645,19 +5353,14 @@
       <c r="AC25" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7729,14 +5432,9 @@
       <c r="AC26" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
@@ -7813,14 +5511,9 @@
       <c r="AC27" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
@@ -7897,14 +5590,9 @@
       <c r="AC28" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -7941,7 +5629,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7981,19 +5669,14 @@
       <c r="AC29" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8065,19 +5748,14 @@
       <c r="AC30" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8149,19 +5827,14 @@
       <c r="AC31" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8228,19 +5901,14 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC32" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -8312,19 +5980,14 @@
         </is>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC33" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -8396,19 +6059,14 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC34" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -8445,7 +6103,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>USA East Coast</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -8480,24 +6138,19 @@
         </is>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC35" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC, CFC for New York only - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -8564,24 +6217,19 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC36" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -8648,24 +6296,19 @@
         </is>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>46113</v>
+        <v>45292</v>
       </c>
       <c r="AC37" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>MED-USA</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD, LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
+          <t>Rates are subject to AMS, ISPS, Wharfage as applicable, CSF, SPD,  LO/LO, CCC - For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -8707,12 +6350,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EFS</t>
+          <t>OPEN TOP IN GAUGE SURCHARGE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>per teu</t>
+          <t>PER_CONTAINER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -8720,11 +6363,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" t="n">
-        <v>20</v>
+      <c r="Q38" t="n">
+        <v>600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>800</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -8732,34 +6375,24 @@
         </is>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | PCE | LO/LO | CCC</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
+          <t>OPEN TOP IN GAUGE SURCHARGE USD 600/20'OT – USD 800/40OT e OT HC</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>Ocean</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -8791,29 +6424,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>per TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>95</v>
-      </c>
-      <c r="J39" t="n">
-        <v>95</v>
+          <t>USD</t>
+        </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -8821,34 +6448,19 @@
         </is>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>45292</v>
+        <v>45839</v>
       </c>
       <c r="AC39" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | PCE | LO/LO | CCC</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -8880,29 +6492,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>ISPS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>per TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>19</v>
-      </c>
-      <c r="J40" t="n">
-        <v>19</v>
+          <t>USD</t>
+        </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -8910,34 +6516,19 @@
         </is>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>45658</v>
+        <v>45839</v>
       </c>
       <c r="AC40" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | PCE | LO/LO | CCC</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -8969,17 +6560,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>WHARFAGE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>per TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -8987,46 +6578,25 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20</v>
-      </c>
       <c r="Z41" t="inlineStr">
         <is>
           <t>nac BIESSE</t>
         </is>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>45782</v>
+        <v>45839</v>
       </c>
       <c r="AC41" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | PCE | LO/LO | CCC</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -9058,29 +6628,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>CSF</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>per TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-      <c r="I42" t="n">
-        <v>665</v>
-      </c>
-      <c r="J42" t="n">
-        <v>665</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -9093,29 +6657,14 @@
       <c r="AC42" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | PCE | LO/LO | CCC</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -9132,12 +6681,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Genova, Livorno, Napoli, Salerno, Gioia Tauro, La Spezia</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, Norfolk</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9147,17 +6696,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EFS</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>per teu</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -9165,46 +6714,25 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>70</v>
-      </c>
-      <c r="J43" t="n">
-        <v>70</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
           <t>nac BIESSE</t>
         </is>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>46143</v>
+        <v>45839</v>
       </c>
       <c r="AC43" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | LO/LO | CCC | CFC for New York only</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -9221,12 +6749,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Genova, Livorno, Napoli, Salerno, Gioia Tauro, La Spezia</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, Norfolk</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,29 +6764,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BRC</t>
+          <t>PCE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>per TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-      <c r="I44" t="n">
-        <v>480</v>
-      </c>
-      <c r="J44" t="n">
-        <v>480</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -9271,29 +6793,14 @@
       <c r="AC44" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>AMS | ISPS | Wharfage | CSF | SPD | LO/LO | CCC | CFC for New York only</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>For dry cntr 10 free working days of perdiem on container only (not fo chassis)</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -9310,12 +6817,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9325,29 +6832,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPEN TOP IN GAUGE SURCHARGE</t>
+          <t>LO/LO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20'OT</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>600</v>
-      </c>
-      <c r="R45" t="n">
-        <v>800</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -9360,19 +6861,14 @@
       <c r="AC45" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>W.Med- USA</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -9389,12 +6885,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LOS ANGELES</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9404,17 +6900,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Surcharge</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PCE</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TEU</t>
+          <t>Per TEU</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -9422,20 +6918,9 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>80</v>
-      </c>
-      <c r="J46" t="n">
-        <v>80</v>
-      </c>
       <c r="Z46" t="inlineStr">
         <is>
           <t>nac BIESSE</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>FOR WEST COAST ONLY</t>
         </is>
       </c>
       <c r="AB46" s="4" t="n">
@@ -9444,19 +6929,14 @@
       <c r="AC46" s="4" t="n">
         <v>46142</v>
       </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>FAK</t>
-        </is>
-      </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>MED-USA</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>Ocean</t>
+          <t>W.Med- USA</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -9468,101 +6948,105 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHARLESTON</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USCHS</t>
+          <t xml:space="preserve">Genova, Livorno, Napoli, Salerno, Gioia Tauro, La Spezia </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>New York, Norfolk</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>USATL</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ONCARRIAGE</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AMN 16</t>
+          <t>CFC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>900</v>
-      </c>
-      <c r="J47" t="n">
-        <v>900</v>
+          <t>Per TEU</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>nac BIESSE</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>For New York only</t>
         </is>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>46023</v>
+        <v>45839</v>
       </c>
       <c r="AC47" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
+        <v>46142</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>W.Med- USA</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>For dry cntr 10free working days of perdiem on container only (not fo chassis)</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
+          <t>NAC BIESSE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SAVANNAH</t>
+          <t>La Spezia</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USSAV</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>LOS ANGELES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>USATL</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ONCARRIAGE</t>
+          <t>ADDITIONAL CHARGE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AMN 16</t>
+          <t>OPEN TOP IN GAUGE SURCHARGE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -9570,1899 +7054,36 @@
           <t>Per Container</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>900</v>
-      </c>
-      <c r="J48" t="n">
-        <v>900</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600</v>
+      </c>
+      <c r="R48" t="n">
+        <v>800</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>nac BIESSE</t>
         </is>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>46023</v>
+        <v>45839</v>
       </c>
       <c r="AC48" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
+        <v>46142</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>AMN</t>
+          <t>W.Med- USA</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>USCHS</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>USBHM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB49" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC49" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>USSAV</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Birmingham</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>USBHM</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB50" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC50" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SAVANNAH</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>USSAV</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>USCLT</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>800</v>
-      </c>
-      <c r="J51" t="n">
-        <v>940</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB51" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC51" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>USCHS</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>USCLT</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>900</v>
-      </c>
-      <c r="J52" t="n">
-        <v>940</v>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB52" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC52" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>USCHI</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>1180</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1150</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB53" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC53" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>USCHI</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1180</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1150</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB54" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC54" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MONTREAL</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>CAMTR</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>USCHI</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1350</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB55" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC55" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>USCVG</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1350</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB56" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC56" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>USCVG</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1190</v>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB57" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC57" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>USCLE</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1350</v>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB58" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC58" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Cleveland</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>USCLE</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1190</v>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB59" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC59" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>USCMH</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1190</v>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB60" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC60" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>USCMH</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2450</v>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB61" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC61" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Council Bluffs</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>USCBF</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I62" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2450</v>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB62" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC62" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Council Bluffs</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>USCBF</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>2650</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2900</v>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB63" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC63" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>HOUSTON</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>USHOU</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Denver</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>USDEN</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB64" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC64" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>USDET</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB65" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC65" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>USDET</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB66" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC66" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MONTREAL</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>CAMTR</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Detroit</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>USDET</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB67" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC67" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>East Saint Louis</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>USESL</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB68" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC68" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>East Saint Louis</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>USESL</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>1690</v>
-      </c>
-      <c r="J69" t="n">
-        <v>1590</v>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB69" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC69" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CHARLESTON</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>USCHS</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Greer</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>USGXX</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J70" t="n">
-        <v>1700</v>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC70" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>USIND</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1700</v>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB71" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC71" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>USMKC</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB72" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC72" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>USMO</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1550</v>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB73" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC73" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>NORFOLK</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>USORF</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>USLUI</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>900</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB74" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC74" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>NEW YORK</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>USNYC</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Louisville</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>USLUI</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ONCARRIAGE</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>AMN 16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Per Container</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1260</v>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>MSC</t>
-        </is>
-      </c>
-      <c r="AB75" s="4" t="n">
-        <v>46023</v>
-      </c>
-      <c r="AC75" s="4" t="n">
-        <v>46203</v>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>AMN</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>[NEW ONCARRIAGE RAMP 2026] Q1 validity from 01/01/26 till 31/03/26 | Q2 till 30/06/2026</t>
+          <t>NAC BIESSE</t>
         </is>
       </c>
     </row>
